--- a/job_application_forms/033_solar_industry_job_application_form--job_application_forms.xlsx
+++ b/job_application_forms/033_solar_industry_job_application_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Primary'}</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'secondary'}</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Secondary'}</t>
+          <t>Secondary</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'high_school_diploma'}</t>
+          <t>high_school_diploma</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'High School Diploma'}</t>
+          <t>High School Diploma</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'doctorate'}</t>
+          <t>doctorate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Doctorate'}</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'american'}</t>
+          <t>american</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'American'}</t>
+          <t>American</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'british'}</t>
+          <t>british</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'British'}</t>
+          <t>British</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'Full Time'}</t>
+          <t>Full Time</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'Part Time'}</t>
+          <t>Part Time</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'Freelance'}</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'looking_for_employment'}</t>
+          <t>looking_for_employment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'Looking for employment'}</t>
+          <t>Looking for employment</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'not_looking_for_employment'}</t>
+          <t>not_looking_for_employment</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'Not looking for employment'}</t>
+          <t>Not looking for employment</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'permanent'}</t>
+          <t>permanent</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'Permanent'}</t>
+          <t>Permanent</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'temporary'}</t>
+          <t>temporary</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'Temporary'}</t>
+          <t>Temporary</t>
         </is>
       </c>
     </row>
